--- a/logs/TimeVarMemory.xlsx
+++ b/logs/TimeVarMemory.xlsx
@@ -8,43 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/Projects/StateFork/logs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B6A900-EA6D-464A-938B-7B6850C191F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8BDB64-5FB9-1449-8591-F6421BEB91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7700" yWindow="500" windowWidth="44580" windowHeight="26880" xr2:uid="{58F692CA-A60A-8148-8992-C00D771DA53A}"/>
+    <workbookView xWindow="820" yWindow="2380" windowWidth="29600" windowHeight="19540" xr2:uid="{58F692CA-A60A-8148-8992-C00D771DA53A}"/>
   </bookViews>
   <sheets>
-    <sheet name="PrintStats" sheetId="3" r:id="rId1"/>
-    <sheet name="c6620" sheetId="2" r:id="rId2"/>
-    <sheet name="brsys" sheetId="1" r:id="rId3"/>
+    <sheet name="vM vF 0Compress" sheetId="8" r:id="rId1"/>
+    <sheet name="0M vF 0Compress" sheetId="7" r:id="rId2"/>
+    <sheet name="vM 0F 0Compress" sheetId="6" r:id="rId3"/>
+    <sheet name="0M 0F vCompress" sheetId="4" r:id="rId4"/>
+    <sheet name="PrintStats" sheetId="3" r:id="rId5"/>
+    <sheet name="c6620" sheetId="2" r:id="rId6"/>
+    <sheet name="brsys" sheetId="1" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">PrintStats!$A$2</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">PrintStats!$B$3</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">PrintStats!$F$5:$H$5</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">PrintStats!$F$6:$H$6</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">PrintStats!$F$7:$H$7</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">PrintStats!$A$2</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">PrintStats!$B$3</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">PrintStats!$D$4</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">PrintStats!$E$5</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">PrintStats!$E$6</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">PrintStats!$E$7</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">PrintStats!$F$1:$H$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">PrintStats!$D$4</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">PrintStats!$F$2:$H$2</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">PrintStats!$F$3:$H$3</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">PrintStats!$F$4:$H$4</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">PrintStats!$F$5:$H$5</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">PrintStats!$F$6:$H$6</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">PrintStats!$F$7:$H$7</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">PrintStats!$E$5</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">PrintStats!$E$6</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">PrintStats!$E$7</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">PrintStats!$F$1:$H$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">PrintStats!$F$2:$H$2</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">PrintStats!$F$3:$H$3</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">PrintStats!$F$4:$H$4</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -66,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="80">
   <si>
     <t>Snapshot (ms)</t>
   </si>
@@ -200,12 +176,6 @@
     <t>Per-page Write Speed</t>
   </si>
   <si>
-    <t>Time it took criu to freeze the process tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time spend transferring memory pages into image files </t>
-  </si>
-  <si>
     <t>podman_restore_duration</t>
   </si>
   <si>
@@ -230,13 +200,88 @@
     <t>Per-page Load Speed</t>
   </si>
   <si>
-    <t>Time took to fork the tree of processes</t>
+    <t>Restore</t>
   </si>
   <si>
-    <t>Total time of restore</t>
+    <t>The same FastAPI target app, but with different sizes of in-memory Numpy arrays added.</t>
   </si>
   <si>
-    <t>Restore</t>
+    <t>Time (ms)</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>gzip</t>
+  </si>
+  <si>
+    <t>zstd</t>
+  </si>
+  <si>
+    <t>0 GB Memory</t>
+  </si>
+  <si>
+    <t>2 GB Memory</t>
+  </si>
+  <si>
+    <t>1 GB Memory</t>
+  </si>
+  <si>
+    <t>Frozen Time</t>
+  </si>
+  <si>
+    <t>Overall Podman Time</t>
+  </si>
+  <si>
+    <t>The FastAPI app with 0 GB memory size, 0 GB local files, and with {different} compression, tested on er078 server</t>
+  </si>
+  <si>
+    <t>Archive Image Size</t>
+  </si>
+  <si>
+    <t>33 MB</t>
+  </si>
+  <si>
+    <t>7.7 MB</t>
+  </si>
+  <si>
+    <t>7.0 MB</t>
+  </si>
+  <si>
+    <t>1.1 GB</t>
+  </si>
+  <si>
+    <t>The FastAPI app with {different} memory size, 0 GB local files, and with no compression, tested on er078 server</t>
+  </si>
+  <si>
+    <t>2.1 GB</t>
+  </si>
+  <si>
+    <t>The FastAPI app with 0 memory size, {different} GB local files, and with no compression, tested on er078 server</t>
+  </si>
+  <si>
+    <t>0 GB Disk</t>
+  </si>
+  <si>
+    <t>1 GB Disk</t>
+  </si>
+  <si>
+    <t>2 GB Disk</t>
+  </si>
+  <si>
+    <t>The FastAPI app with  {different}  memory size, {different} GB local files, and with no compression, tested on er078 server</t>
+  </si>
+  <si>
+    <t>0 GB Memory Disk</t>
+  </si>
+  <si>
+    <t>1 GB Memory Disk</t>
+  </si>
+  <si>
+    <t>2 GB Memory Disk</t>
+  </si>
+  <si>
+    <t>4.1 GB</t>
   </si>
 </sst>
 </file>
@@ -247,7 +292,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,6 +319,13 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -351,7 +403,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -667,11 +719,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -686,12 +851,6 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -732,14 +891,8 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -756,9 +909,6 @@
     <xf numFmtId="164" fontId="2" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -771,12 +921,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -785,12 +929,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
@@ -801,16 +939,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -825,13 +957,31 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -839,6 +989,129 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -883,7 +1156,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$A$2</c:f>
+              <c:f>PrintStats!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -962,7 +1235,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$F$1</c:f>
+              <c:f>PrintStats!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -973,7 +1246,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$F$2</c:f>
+              <c:f>PrintStats!$F$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -994,7 +1267,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$B$3</c:f>
+              <c:f>PrintStats!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -1072,7 +1345,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$F$1</c:f>
+              <c:f>PrintStats!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1083,7 +1356,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$F$3</c:f>
+              <c:f>PrintStats!$F$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1104,7 +1377,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$D$4</c:f>
+              <c:f>PrintStats!$D$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -1182,7 +1455,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$F$1</c:f>
+              <c:f>PrintStats!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1193,7 +1466,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$F$4</c:f>
+              <c:f>PrintStats!$F$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1214,7 +1487,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$5</c:f>
+              <c:f>PrintStats!$E$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1295,7 +1568,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$F$1</c:f>
+              <c:f>PrintStats!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1306,7 +1579,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$F$5</c:f>
+              <c:f>PrintStats!$F$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1327,7 +1600,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$6</c:f>
+              <c:f>PrintStats!$E$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1408,7 +1681,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$F$1</c:f>
+              <c:f>PrintStats!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1419,7 +1692,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$F$6</c:f>
+              <c:f>PrintStats!$F$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1440,7 +1713,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$7</c:f>
+              <c:f>PrintStats!$E$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1521,7 +1794,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$F$1</c:f>
+              <c:f>PrintStats!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1532,7 +1805,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$F$7</c:f>
+              <c:f>PrintStats!$F$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5266,7 +5539,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$A$2</c:f>
+              <c:f>PrintStats!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -5344,7 +5617,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$G$1</c:f>
+              <c:f>PrintStats!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5355,7 +5628,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$G$2</c:f>
+              <c:f>PrintStats!$G$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5376,7 +5649,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$B$3</c:f>
+              <c:f>PrintStats!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -5454,7 +5727,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$G$1</c:f>
+              <c:f>PrintStats!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5465,7 +5738,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$G$3</c:f>
+              <c:f>PrintStats!$G$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5486,7 +5759,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$D$4</c:f>
+              <c:f>PrintStats!$D$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -5564,7 +5837,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$G$1</c:f>
+              <c:f>PrintStats!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5575,7 +5848,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$G$4</c:f>
+              <c:f>PrintStats!$G$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5596,7 +5869,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$5</c:f>
+              <c:f>PrintStats!$E$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5677,7 +5950,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$G$1</c:f>
+              <c:f>PrintStats!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5688,7 +5961,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$G$5</c:f>
+              <c:f>PrintStats!$G$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5709,7 +5982,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$6</c:f>
+              <c:f>PrintStats!$E$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5790,7 +6063,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$G$1</c:f>
+              <c:f>PrintStats!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5801,7 +6074,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$G$6</c:f>
+              <c:f>PrintStats!$G$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5822,7 +6095,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$7</c:f>
+              <c:f>PrintStats!$E$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5903,7 +6176,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$G$1</c:f>
+              <c:f>PrintStats!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5914,7 +6187,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$G$7</c:f>
+              <c:f>PrintStats!$G$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6130,7 +6403,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$2</c:f>
+              <c:f>PrintStats!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6211,7 +6484,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$H$1</c:f>
+              <c:f>PrintStats!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6222,7 +6495,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$H$2</c:f>
+              <c:f>PrintStats!$H$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6243,7 +6516,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$3</c:f>
+              <c:f>PrintStats!$E$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6345,7 +6618,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$H$1</c:f>
+              <c:f>PrintStats!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6356,7 +6629,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$H$3</c:f>
+              <c:f>PrintStats!$H$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6377,7 +6650,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$4</c:f>
+              <c:f>PrintStats!$E$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6458,7 +6731,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$H$1</c:f>
+              <c:f>PrintStats!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6469,7 +6742,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$H$4</c:f>
+              <c:f>PrintStats!$H$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6490,7 +6763,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$5</c:f>
+              <c:f>PrintStats!$E$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6571,7 +6844,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$H$1</c:f>
+              <c:f>PrintStats!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6582,7 +6855,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$H$5</c:f>
+              <c:f>PrintStats!$H$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6603,7 +6876,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$6</c:f>
+              <c:f>PrintStats!$E$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6684,7 +6957,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$H$1</c:f>
+              <c:f>PrintStats!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6695,7 +6968,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$H$6</c:f>
+              <c:f>PrintStats!$H$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6716,7 +6989,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$7</c:f>
+              <c:f>PrintStats!$E$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6797,7 +7070,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$H$1</c:f>
+              <c:f>PrintStats!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6808,7 +7081,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$H$7</c:f>
+              <c:f>PrintStats!$H$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7025,7 +7298,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$2</c:f>
+              <c:f>PrintStats!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7106,7 +7379,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$I$1</c:f>
+              <c:f>PrintStats!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7117,7 +7390,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$I$2</c:f>
+              <c:f>PrintStats!$I$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7138,7 +7411,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$3</c:f>
+              <c:f>PrintStats!$E$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7240,7 +7513,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$I$1</c:f>
+              <c:f>PrintStats!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7251,7 +7524,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$I$3</c:f>
+              <c:f>PrintStats!$I$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7272,7 +7545,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$4</c:f>
+              <c:f>PrintStats!$E$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7353,7 +7626,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$I$1</c:f>
+              <c:f>PrintStats!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7364,7 +7637,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$I$4</c:f>
+              <c:f>PrintStats!$I$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7385,7 +7658,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$5</c:f>
+              <c:f>PrintStats!$E$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7466,7 +7739,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$I$1</c:f>
+              <c:f>PrintStats!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7477,7 +7750,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$I$5</c:f>
+              <c:f>PrintStats!$I$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7498,7 +7771,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$6</c:f>
+              <c:f>PrintStats!$E$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7579,7 +7852,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$I$1</c:f>
+              <c:f>PrintStats!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7590,7 +7863,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$I$6</c:f>
+              <c:f>PrintStats!$I$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7611,7 +7884,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$E$7</c:f>
+              <c:f>PrintStats!$E$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7692,7 +7965,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$I$1</c:f>
+              <c:f>PrintStats!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7703,7 +7976,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$I$7</c:f>
+              <c:f>PrintStats!$I$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7920,7 +8193,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$2</c:f>
+              <c:f>PrintStats!$N$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8036,7 +8309,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$Q$1</c:f>
+              <c:f>PrintStats!$O$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8047,7 +8320,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$Q$2</c:f>
+              <c:f>PrintStats!$O$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8068,7 +8341,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$3</c:f>
+              <c:f>PrintStats!$N$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8150,7 +8423,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$Q$1</c:f>
+              <c:f>PrintStats!$O$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8161,7 +8434,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$Q$3</c:f>
+              <c:f>PrintStats!$O$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8182,7 +8455,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$4</c:f>
+              <c:f>PrintStats!$N$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8261,7 +8534,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$Q$1</c:f>
+              <c:f>PrintStats!$O$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8272,7 +8545,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$Q$4</c:f>
+              <c:f>PrintStats!$O$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8293,7 +8566,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$5</c:f>
+              <c:f>PrintStats!$N$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8375,7 +8648,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$Q$1</c:f>
+              <c:f>PrintStats!$O$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8386,7 +8659,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$Q$5</c:f>
+              <c:f>PrintStats!$O$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8602,7 +8875,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$2</c:f>
+              <c:f>PrintStats!$N$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8684,7 +8957,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$R$1</c:f>
+              <c:f>PrintStats!$P$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8695,7 +8968,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$R$2</c:f>
+              <c:f>PrintStats!$P$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8716,7 +8989,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$3</c:f>
+              <c:f>PrintStats!$N$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8798,7 +9071,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$R$1</c:f>
+              <c:f>PrintStats!$P$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8809,7 +9082,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$R$3</c:f>
+              <c:f>PrintStats!$P$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8830,7 +9103,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$4</c:f>
+              <c:f>PrintStats!$N$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8931,7 +9204,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$R$1</c:f>
+              <c:f>PrintStats!$P$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8942,7 +9215,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$R$4</c:f>
+              <c:f>PrintStats!$P$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8963,7 +9236,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$5</c:f>
+              <c:f>PrintStats!$N$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9045,7 +9318,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$R$1</c:f>
+              <c:f>PrintStats!$P$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9056,7 +9329,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$R$5</c:f>
+              <c:f>PrintStats!$P$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -9273,7 +9546,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$2</c:f>
+              <c:f>PrintStats!$N$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9355,7 +9628,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$S$1</c:f>
+              <c:f>PrintStats!$Q$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9366,7 +9639,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$S$2</c:f>
+              <c:f>PrintStats!$Q$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -9387,7 +9660,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$3</c:f>
+              <c:f>PrintStats!$N$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9469,7 +9742,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$S$1</c:f>
+              <c:f>PrintStats!$Q$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9480,7 +9753,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$S$3</c:f>
+              <c:f>PrintStats!$Q$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -9501,7 +9774,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$4</c:f>
+              <c:f>PrintStats!$N$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9602,7 +9875,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$S$1</c:f>
+              <c:f>PrintStats!$Q$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9613,7 +9886,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$S$4</c:f>
+              <c:f>PrintStats!$Q$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -9634,7 +9907,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$5</c:f>
+              <c:f>PrintStats!$N$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9716,7 +9989,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$S$1</c:f>
+              <c:f>PrintStats!$Q$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9727,7 +10000,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$S$5</c:f>
+              <c:f>PrintStats!$Q$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -9944,7 +10217,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$2</c:f>
+              <c:f>PrintStats!$N$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10045,7 +10318,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$T$1</c:f>
+              <c:f>PrintStats!$R$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10056,7 +10329,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$T$2</c:f>
+              <c:f>PrintStats!$R$4</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -10077,7 +10350,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$3</c:f>
+              <c:f>PrintStats!$N$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10159,7 +10432,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$T$1</c:f>
+              <c:f>PrintStats!$R$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10170,7 +10443,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$T$3</c:f>
+              <c:f>PrintStats!$R$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -10191,7 +10464,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$4</c:f>
+              <c:f>PrintStats!$N$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10292,7 +10565,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$T$1</c:f>
+              <c:f>PrintStats!$R$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10303,7 +10576,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$T$4</c:f>
+              <c:f>PrintStats!$R$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -10324,7 +10597,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>PrintStats!$P$5</c:f>
+              <c:f>PrintStats!$N$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10406,7 +10679,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PrintStats!$T$1</c:f>
+              <c:f>PrintStats!$R$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10417,7 +10690,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PrintStats!$T$5</c:f>
+              <c:f>PrintStats!$R$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000</c:formatCode>
                 <c:ptCount val="1"/>
@@ -18039,15 +18312,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1435100</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:colOff>1485900</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -18062,7 +18335,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="228600" y="4394200"/>
+          <a:off x="279400" y="7594600"/>
           <a:ext cx="10312400" cy="5486400"/>
           <a:chOff x="139700" y="6946900"/>
           <a:chExt cx="11531600" cy="5486400"/>
@@ -18163,15 +18436,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>279400</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -18187,8 +18460,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12103100" y="3327400"/>
-          <a:ext cx="10731500" cy="5486400"/>
+          <a:off x="10693400" y="6134100"/>
+          <a:ext cx="11023600" cy="5486400"/>
           <a:chOff x="13322300" y="5892800"/>
           <a:chExt cx="11595100" cy="5486400"/>
         </a:xfrm>
@@ -18767,624 +19040,2881 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787533C2-EB56-4A4E-A56E-7B1B185309E4}">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="3.83203125" style="9" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" style="9" customWidth="1"/>
+    <col min="9" max="11" width="3.83203125" style="9" customWidth="1"/>
+    <col min="12" max="16" width="20.83203125" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+    </row>
+    <row r="2" spans="1:18" ht="20" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="18">
+        <f>(E13-E14)/1000</f>
+        <v>157.58699999999999</v>
+      </c>
+      <c r="F4" s="15">
+        <f>(F13-F14)/1000</f>
+        <v>8559.6569999999992</v>
+      </c>
+      <c r="G4" s="24">
+        <f>(G13-G14)/1000</f>
+        <v>14864.57</v>
+      </c>
+      <c r="I4" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="15">
+        <f>(M13-M14)/1000</f>
+        <v>225.934</v>
+      </c>
+      <c r="N4" s="15">
+        <f>(N13-N14)/1000</f>
+        <v>7602.8940000000002</v>
+      </c>
+      <c r="O4" s="24">
+        <f>(O13-O14)/1000</f>
+        <v>13854.823</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="57"/>
+      <c r="B5" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="14">
+        <f>(E14-E15-E16)/1000</f>
+        <v>21.718</v>
+      </c>
+      <c r="F5" s="14">
+        <f>(F14-F15-F16)/1000</f>
+        <v>21.911999999999999</v>
+      </c>
+      <c r="G5" s="25">
+        <f>(G14-G15-G16)/1000</f>
+        <v>21.655000000000001</v>
+      </c>
+      <c r="I5" s="73"/>
+      <c r="J5" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="77"/>
+      <c r="L5" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="14">
+        <f>(M14-M15-M16)/1000</f>
+        <v>112.444</v>
+      </c>
+      <c r="N5" s="14">
+        <f>(N14-N15-N16)/1000</f>
+        <v>104.63800000000001</v>
+      </c>
+      <c r="O5" s="25">
+        <f>(O14-O15-O16)/1000</f>
+        <v>107.994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="57"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="13">
+        <f>E15/1000</f>
+        <v>100.741</v>
+      </c>
+      <c r="F6" s="13">
+        <f>F15/1000</f>
+        <v>104.209</v>
+      </c>
+      <c r="G6" s="26">
+        <f>G15/1000</f>
+        <v>104.349</v>
+      </c>
+      <c r="I6" s="73"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="13">
+        <f>M15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N6" s="13">
+        <f>N15/1000</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="O6" s="26">
+        <f>O15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="57"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="10">
+        <f>E16/1000</f>
+        <v>234.65700000000001</v>
+      </c>
+      <c r="F7" s="10">
+        <f>F16/1000</f>
+        <v>1612.7149999999999</v>
+      </c>
+      <c r="G7" s="27">
+        <f>G16/1000</f>
+        <v>2965.462</v>
+      </c>
+      <c r="I7" s="73"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="10">
+        <f>M16/1000</f>
+        <v>159.84100000000001</v>
+      </c>
+      <c r="N7" s="10">
+        <f>N16/1000</f>
+        <v>828.18700000000001</v>
+      </c>
+      <c r="O7" s="27">
+        <f>O16/1000</f>
+        <v>1421.4549999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="66"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="65">
+        <f>E7/E20</f>
+        <v>2.8627180675857022E-2</v>
+      </c>
+      <c r="F8" s="65">
+        <f t="shared" ref="F8:G8" si="0">F7/F20</f>
+        <v>5.9336367516336017E-3</v>
+      </c>
+      <c r="G8" s="67">
+        <f t="shared" si="0"/>
+        <v>5.5539548673345356E-3</v>
+      </c>
+      <c r="I8" s="73"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="65">
+        <f>M7/M17</f>
+        <v>1.9499939002073932E-2</v>
+      </c>
+      <c r="N8" s="65">
+        <f>N7/N17</f>
+        <v>3.0471353093542122E-3</v>
+      </c>
+      <c r="O8" s="67">
+        <f>O7/O17</f>
+        <v>2.6622148305886274E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="15">
+        <f>E13/1000</f>
+        <v>514.70299999999997</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" ref="F9:G9" si="1">F13/1000</f>
+        <v>10298.493</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="1"/>
+        <v>17956.036</v>
+      </c>
+      <c r="I9" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="70">
+        <f>M13/1000</f>
+        <v>498.22399999999999</v>
+      </c>
+      <c r="N9" s="70">
+        <f t="shared" ref="N9:O9" si="2">N13/1000</f>
+        <v>8535.7250000000004</v>
+      </c>
+      <c r="O9" s="71">
+        <f t="shared" si="2"/>
+        <v>15384.277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+    </row>
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="95"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="92"/>
+    </row>
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="L12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+    </row>
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="42">
+        <v>514703</v>
+      </c>
+      <c r="F13" s="42">
+        <v>10298493</v>
+      </c>
+      <c r="G13" s="42">
+        <v>17956036</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="42">
+        <v>498224</v>
+      </c>
+      <c r="N13" s="42">
+        <v>8535725</v>
+      </c>
+      <c r="O13" s="42">
+        <v>15384277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="42">
+        <v>357116</v>
+      </c>
+      <c r="F14" s="42">
+        <v>1738836</v>
+      </c>
+      <c r="G14" s="42">
+        <v>3091466</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="42">
+        <v>272290</v>
+      </c>
+      <c r="N14" s="42">
+        <v>932831</v>
+      </c>
+      <c r="O14" s="42">
+        <v>1529454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="42">
+        <v>100741</v>
+      </c>
+      <c r="F15" s="42">
+        <v>104209</v>
+      </c>
+      <c r="G15" s="42">
+        <v>104349</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="42">
+        <v>5</v>
+      </c>
+      <c r="N15" s="42">
+        <v>6</v>
+      </c>
+      <c r="O15" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="42">
+        <v>234657</v>
+      </c>
+      <c r="F16" s="42">
+        <v>1612715</v>
+      </c>
+      <c r="G16" s="42">
+        <v>2965462</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="42">
+        <v>159841</v>
+      </c>
+      <c r="N16" s="42">
+        <v>828187</v>
+      </c>
+      <c r="O16" s="42">
+        <v>1421455</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="42">
+        <v>54299</v>
+      </c>
+      <c r="F17" s="42">
+        <v>1361462</v>
+      </c>
+      <c r="G17" s="42">
+        <v>2703202</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="42">
+        <v>8197</v>
+      </c>
+      <c r="N17" s="42">
+        <v>271792</v>
+      </c>
+      <c r="O17" s="42">
+        <v>533937</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="42">
+        <v>40982</v>
+      </c>
+      <c r="F18" s="42">
+        <v>1311794</v>
+      </c>
+      <c r="G18" s="42">
+        <v>2611762</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="42">
+        <v>8366</v>
+      </c>
+      <c r="F19" s="42">
+        <v>272147</v>
+      </c>
+      <c r="G19" s="42">
+        <v>534290</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="42">
+        <v>8197</v>
+      </c>
+      <c r="F20" s="42">
+        <v>271792</v>
+      </c>
+      <c r="G20" s="42">
+        <v>533937</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="I4:I8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="K6:K8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456D27D7-C609-A24C-9ECC-6CC4EA0FA956}">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="3.83203125" style="9" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" style="9" customWidth="1"/>
+    <col min="9" max="11" width="3.83203125" style="9" customWidth="1"/>
+    <col min="12" max="16" width="20.83203125" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+    </row>
+    <row r="2" spans="1:18" ht="20" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="18">
+        <f>(E13-E14)/1000</f>
+        <v>157.58699999999999</v>
+      </c>
+      <c r="F4" s="15">
+        <f>(F13-F14)/1000</f>
+        <v>5537.4849999999997</v>
+      </c>
+      <c r="G4" s="24">
+        <f>(G13-G14)/1000</f>
+        <v>11132.040999999999</v>
+      </c>
+      <c r="I4" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="15">
+        <f>(M13-M14)/1000</f>
+        <v>225.934</v>
+      </c>
+      <c r="N4" s="15">
+        <f>(N13-N14)/1000</f>
+        <v>5005.6540000000005</v>
+      </c>
+      <c r="O4" s="24">
+        <f>(O13-O14)/1000</f>
+        <v>9892.0969999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="57"/>
+      <c r="B5" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="14">
+        <f>(E14-E15-E16)/1000</f>
+        <v>21.718</v>
+      </c>
+      <c r="F5" s="14">
+        <f>(F14-F15-F16)/1000</f>
+        <v>21.344000000000001</v>
+      </c>
+      <c r="G5" s="25">
+        <f>(G14-G15-G16)/1000</f>
+        <v>21.765000000000001</v>
+      </c>
+      <c r="I5" s="73"/>
+      <c r="J5" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="77"/>
+      <c r="L5" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="14">
+        <f>(M14-M15-M16)/1000</f>
+        <v>112.444</v>
+      </c>
+      <c r="N5" s="14">
+        <f>(N14-N15-N16)/1000</f>
+        <v>100.85899999999999</v>
+      </c>
+      <c r="O5" s="25">
+        <f>(O14-O15-O16)/1000</f>
+        <v>109.545</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="57"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="13">
+        <f>E15/1000</f>
+        <v>100.741</v>
+      </c>
+      <c r="F6" s="13">
+        <f>F15/1000</f>
+        <v>100.617</v>
+      </c>
+      <c r="G6" s="26">
+        <f>G15/1000</f>
+        <v>100.834</v>
+      </c>
+      <c r="I6" s="73"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="13">
+        <f>M15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N6" s="13">
+        <f>N15/1000</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="O6" s="26">
+        <f>O15/1000</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="57"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="10">
+        <f>E16/1000</f>
+        <v>234.65700000000001</v>
+      </c>
+      <c r="F7" s="10">
+        <f>F16/1000</f>
+        <v>258.09899999999999</v>
+      </c>
+      <c r="G7" s="27">
+        <f>G16/1000</f>
+        <v>250.589</v>
+      </c>
+      <c r="I7" s="73"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="10">
+        <f>M16/1000</f>
+        <v>159.84100000000001</v>
+      </c>
+      <c r="N7" s="10">
+        <f>N16/1000</f>
+        <v>183.08199999999999</v>
+      </c>
+      <c r="O7" s="27">
+        <f>O16/1000</f>
+        <v>180.863</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="66"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="65">
+        <f>E7/E20</f>
+        <v>2.8627180675857022E-2</v>
+      </c>
+      <c r="F8" s="65">
+        <f t="shared" ref="F8:G8" si="0">F7/F20</f>
+        <v>3.0500945402978017E-2</v>
+      </c>
+      <c r="G8" s="67">
+        <f t="shared" si="0"/>
+        <v>2.9711761916054066E-2</v>
+      </c>
+      <c r="I8" s="73"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="65">
+        <f>M7/M17</f>
+        <v>1.9499939002073932E-2</v>
+      </c>
+      <c r="N8" s="65">
+        <f>N7/N17</f>
+        <v>2.1635783502718033E-2</v>
+      </c>
+      <c r="O8" s="67">
+        <f>O7/O17</f>
+        <v>2.1444510315390089E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="15">
+        <f>E13/1000</f>
+        <v>514.70299999999997</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" ref="F9:G9" si="1">F13/1000</f>
+        <v>5917.5450000000001</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="1"/>
+        <v>11505.228999999999</v>
+      </c>
+      <c r="I9" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="70">
+        <f>M13/1000</f>
+        <v>498.22399999999999</v>
+      </c>
+      <c r="N9" s="70">
+        <f t="shared" ref="N9:O9" si="2">N13/1000</f>
+        <v>5289.5990000000002</v>
+      </c>
+      <c r="O9" s="71">
+        <f t="shared" si="2"/>
+        <v>10182.509</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+    </row>
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="95"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="92"/>
+    </row>
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="L12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+    </row>
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="42">
+        <v>514703</v>
+      </c>
+      <c r="F13" s="42">
+        <v>5917545</v>
+      </c>
+      <c r="G13" s="42">
+        <v>11505229</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="42">
+        <v>498224</v>
+      </c>
+      <c r="N13" s="42">
+        <v>5289599</v>
+      </c>
+      <c r="O13" s="42">
+        <v>10182509</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="42">
+        <v>357116</v>
+      </c>
+      <c r="F14" s="42">
+        <v>380060</v>
+      </c>
+      <c r="G14" s="42">
+        <v>373188</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="42">
+        <v>272290</v>
+      </c>
+      <c r="N14" s="42">
+        <v>283945</v>
+      </c>
+      <c r="O14" s="42">
+        <v>290412</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="42">
+        <v>100741</v>
+      </c>
+      <c r="F15" s="42">
+        <v>100617</v>
+      </c>
+      <c r="G15" s="42">
+        <v>100834</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="42">
+        <v>5</v>
+      </c>
+      <c r="N15" s="42">
+        <v>4</v>
+      </c>
+      <c r="O15" s="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="42">
+        <v>234657</v>
+      </c>
+      <c r="F16" s="42">
+        <v>258099</v>
+      </c>
+      <c r="G16" s="42">
+        <v>250589</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="42">
+        <v>159841</v>
+      </c>
+      <c r="N16" s="42">
+        <v>183082</v>
+      </c>
+      <c r="O16" s="42">
+        <v>180863</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="42">
+        <v>54299</v>
+      </c>
+      <c r="F17" s="42">
+        <v>54954</v>
+      </c>
+      <c r="G17" s="42">
+        <v>54960</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="42">
+        <v>8197</v>
+      </c>
+      <c r="N17" s="42">
+        <v>8462</v>
+      </c>
+      <c r="O17" s="42">
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="42">
+        <v>40982</v>
+      </c>
+      <c r="F18" s="42">
+        <v>41709</v>
+      </c>
+      <c r="G18" s="42">
+        <v>41753</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="42">
+        <v>8366</v>
+      </c>
+      <c r="F19" s="42">
+        <v>8645</v>
+      </c>
+      <c r="G19" s="42">
+        <v>8613</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="42">
+        <v>8197</v>
+      </c>
+      <c r="F20" s="42">
+        <v>8462</v>
+      </c>
+      <c r="G20" s="42">
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="I4:I8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="K6:K8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA846F9-2467-434C-A659-1CC1DEE101CF}">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="3.83203125" style="9" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" style="9" customWidth="1"/>
+    <col min="9" max="11" width="3.83203125" style="9" customWidth="1"/>
+    <col min="12" max="16" width="20.83203125" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+    </row>
+    <row r="2" spans="1:18" ht="20" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="18">
+        <f>(E13-E14)/1000</f>
+        <v>157.58699999999999</v>
+      </c>
+      <c r="F4" s="15">
+        <f>(F13-F14)/1000</f>
+        <v>3243.4209999999998</v>
+      </c>
+      <c r="G4" s="24">
+        <f>(G13-G14)/1000</f>
+        <v>6144.62</v>
+      </c>
+      <c r="I4" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="15">
+        <f>(M13-M14)/1000</f>
+        <v>225.934</v>
+      </c>
+      <c r="N4" s="15">
+        <f>(N13-N14)/1000</f>
+        <v>2818.37</v>
+      </c>
+      <c r="O4" s="24">
+        <f>(O13-O14)/1000</f>
+        <v>4628.0370000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="57"/>
+      <c r="B5" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="14">
+        <f>(E14-E15-E16)/1000</f>
+        <v>21.718</v>
+      </c>
+      <c r="F5" s="14">
+        <f>(F14-F15-F16)/1000</f>
+        <v>22.152000000000001</v>
+      </c>
+      <c r="G5" s="25">
+        <f>(G14-G15-G16)/1000</f>
+        <v>20.756</v>
+      </c>
+      <c r="I5" s="73"/>
+      <c r="J5" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="77"/>
+      <c r="L5" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="14">
+        <f>(M14-M15-M16)/1000</f>
+        <v>112.444</v>
+      </c>
+      <c r="N5" s="14">
+        <f>(N14-N15-N16)/1000</f>
+        <v>129.994</v>
+      </c>
+      <c r="O5" s="25">
+        <f>(O14-O15-O16)/1000</f>
+        <v>135.43100000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="57"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="13">
+        <f>E15/1000</f>
+        <v>100.741</v>
+      </c>
+      <c r="F6" s="13">
+        <f>F15/1000</f>
+        <v>104.221</v>
+      </c>
+      <c r="G6" s="26">
+        <f>G15/1000</f>
+        <v>104.312</v>
+      </c>
+      <c r="I6" s="73"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="13">
+        <f>M15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N6" s="13">
+        <f>N15/1000</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="O6" s="26">
+        <f>O15/1000</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="57"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="10">
+        <f>E16/1000</f>
+        <v>234.65700000000001</v>
+      </c>
+      <c r="F7" s="10">
+        <f>F16/1000</f>
+        <v>1621.3979999999999</v>
+      </c>
+      <c r="G7" s="27">
+        <f>G16/1000</f>
+        <v>2966.873</v>
+      </c>
+      <c r="I7" s="73"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="10">
+        <f>M16/1000</f>
+        <v>159.84100000000001</v>
+      </c>
+      <c r="N7" s="10">
+        <f>N16/1000</f>
+        <v>837.08299999999997</v>
+      </c>
+      <c r="O7" s="27">
+        <f>O16/1000</f>
+        <v>1402.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="66"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="65">
+        <f>E7/E20</f>
+        <v>2.8627180675857022E-2</v>
+      </c>
+      <c r="F8" s="65">
+        <f t="shared" ref="F8:G8" si="0">F7/F20</f>
+        <v>5.9729239882412742E-3</v>
+      </c>
+      <c r="G8" s="67">
+        <f t="shared" si="0"/>
+        <v>5.5600651419404649E-3</v>
+      </c>
+      <c r="I8" s="73"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="65">
+        <f>M7/M17</f>
+        <v>1.9499939002073932E-2</v>
+      </c>
+      <c r="N8" s="65">
+        <f>N7/N17</f>
+        <v>3.0836556668066514E-3</v>
+      </c>
+      <c r="O8" s="67">
+        <f>O7/O17</f>
+        <v>2.6281287246722289E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="15">
+        <f>E13/1000</f>
+        <v>514.70299999999997</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" ref="F9:G9" si="1">F13/1000</f>
+        <v>4991.192</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="1"/>
+        <v>9236.5609999999997</v>
+      </c>
+      <c r="I9" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="70">
+        <f>M13/1000</f>
+        <v>498.22399999999999</v>
+      </c>
+      <c r="N9" s="70">
+        <f t="shared" ref="N9:O9" si="2">N13/1000</f>
+        <v>3785.451</v>
+      </c>
+      <c r="O9" s="71">
+        <f t="shared" si="2"/>
+        <v>6165.8519999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+    </row>
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="95"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="92"/>
+    </row>
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="L12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+    </row>
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="42">
+        <v>514703</v>
+      </c>
+      <c r="F13" s="42">
+        <v>4991192</v>
+      </c>
+      <c r="G13" s="42">
+        <v>9236561</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="42">
+        <v>498224</v>
+      </c>
+      <c r="N13" s="42">
+        <v>3785451</v>
+      </c>
+      <c r="O13" s="42">
+        <v>6165852</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="42">
+        <v>357116</v>
+      </c>
+      <c r="F14" s="42">
+        <v>1747771</v>
+      </c>
+      <c r="G14" s="42">
+        <v>3091941</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="42">
+        <v>272290</v>
+      </c>
+      <c r="N14" s="42">
+        <v>967081</v>
+      </c>
+      <c r="O14" s="42">
+        <v>1537815</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="42">
+        <v>100741</v>
+      </c>
+      <c r="F15" s="42">
+        <v>104221</v>
+      </c>
+      <c r="G15" s="42">
+        <v>104312</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="42">
+        <v>5</v>
+      </c>
+      <c r="N15" s="42">
+        <v>4</v>
+      </c>
+      <c r="O15" s="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="42">
+        <v>234657</v>
+      </c>
+      <c r="F16" s="42">
+        <v>1621398</v>
+      </c>
+      <c r="G16" s="42">
+        <v>2966873</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="42">
+        <v>159841</v>
+      </c>
+      <c r="N16" s="42">
+        <v>837083</v>
+      </c>
+      <c r="O16" s="42">
+        <v>1402380</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="42">
+        <v>54299</v>
+      </c>
+      <c r="F17" s="42">
+        <v>1373653</v>
+      </c>
+      <c r="G17" s="42">
+        <v>2712983</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="42">
+        <v>8197</v>
+      </c>
+      <c r="N17" s="42">
+        <v>271458</v>
+      </c>
+      <c r="O17" s="42">
+        <v>533604</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="42">
+        <v>40982</v>
+      </c>
+      <c r="F18" s="42">
+        <v>1324750</v>
+      </c>
+      <c r="G18" s="42">
+        <v>2624377</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="42">
+        <v>8366</v>
+      </c>
+      <c r="F19" s="42">
+        <v>271817</v>
+      </c>
+      <c r="G19" s="42">
+        <v>533950</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="42">
+        <v>8197</v>
+      </c>
+      <c r="F20" s="42">
+        <v>271458</v>
+      </c>
+      <c r="G20" s="42">
+        <v>533604</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="I4:I8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="K6:K8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD66CD0-3101-CC4F-A29D-F2726A08E908}">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="3.83203125" style="9" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" style="9" customWidth="1"/>
+    <col min="9" max="11" width="3.83203125" style="9" customWidth="1"/>
+    <col min="12" max="16" width="20.83203125" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+    </row>
+    <row r="2" spans="1:18" ht="20" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="18">
+        <f>(E13-E14)/1000</f>
+        <v>157.58699999999999</v>
+      </c>
+      <c r="F4" s="15">
+        <f>(F13-F14)/1000</f>
+        <v>178.739</v>
+      </c>
+      <c r="G4" s="24">
+        <f>(G13-G14)/1000</f>
+        <v>501.911</v>
+      </c>
+      <c r="I4" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="15">
+        <f>(M13-M14)/1000</f>
+        <v>225.934</v>
+      </c>
+      <c r="N4" s="15">
+        <f>(N13-N14)/1000</f>
+        <v>617.65899999999999</v>
+      </c>
+      <c r="O4" s="24">
+        <f>(O13-O14)/1000</f>
+        <v>437.40699999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="57"/>
+      <c r="B5" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="14">
+        <f>(E14-E15-E16)/1000</f>
+        <v>21.718</v>
+      </c>
+      <c r="F5" s="14">
+        <f>(F14-F15-F16)/1000</f>
+        <v>21.530999999999999</v>
+      </c>
+      <c r="G5" s="25">
+        <f>(G14-G15-G16)/1000</f>
+        <v>21.811</v>
+      </c>
+      <c r="I5" s="73"/>
+      <c r="J5" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="77"/>
+      <c r="L5" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="14">
+        <f>(M14-M15-M16)/1000</f>
+        <v>112.444</v>
+      </c>
+      <c r="N5" s="14">
+        <f>(N14-N15-N16)/1000</f>
+        <v>92.364000000000004</v>
+      </c>
+      <c r="O5" s="25">
+        <f>(O14-O15-O16)/1000</f>
+        <v>96.349000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="57"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="13">
+        <f>E15/1000</f>
+        <v>100.741</v>
+      </c>
+      <c r="F6" s="13">
+        <f>F15/1000</f>
+        <v>100.621</v>
+      </c>
+      <c r="G6" s="26">
+        <f>G15/1000</f>
+        <v>100.64</v>
+      </c>
+      <c r="I6" s="73"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="13">
+        <f>M15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N6" s="13">
+        <f>N15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O6" s="26">
+        <f>O15/1000</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="57"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="10">
+        <f>E16/1000</f>
+        <v>234.65700000000001</v>
+      </c>
+      <c r="F7" s="10">
+        <f>F16/1000</f>
+        <v>262.86700000000002</v>
+      </c>
+      <c r="G7" s="27">
+        <f>G16/1000</f>
+        <v>266.21800000000002</v>
+      </c>
+      <c r="I7" s="73"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="10">
+        <f>M16/1000</f>
+        <v>159.84100000000001</v>
+      </c>
+      <c r="N7" s="10">
+        <f>N16/1000</f>
+        <v>180.54400000000001</v>
+      </c>
+      <c r="O7" s="27">
+        <f>O16/1000</f>
+        <v>185.422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="66"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="65">
+        <f>E7/E20</f>
+        <v>2.8627180675857022E-2</v>
+      </c>
+      <c r="F8" s="65">
+        <f t="shared" ref="F8:G8" si="0">F7/F20</f>
+        <v>3.2068683664755397E-2</v>
+      </c>
+      <c r="G8" s="67">
+        <f t="shared" si="0"/>
+        <v>3.2477491765279982E-2</v>
+      </c>
+      <c r="I8" s="73"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="65">
+        <f>M7/M17</f>
+        <v>1.9499939002073932E-2</v>
+      </c>
+      <c r="N8" s="65">
+        <f>N7/N17</f>
+        <v>2.2025619128949618E-2</v>
+      </c>
+      <c r="O8" s="67">
+        <f>O7/O17</f>
+        <v>2.2620714895693547E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="15">
+        <f>E13/1000</f>
+        <v>514.70299999999997</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" ref="F9:G9" si="1">F13/1000</f>
+        <v>563.75800000000004</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="1"/>
+        <v>890.58</v>
+      </c>
+      <c r="I9" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="70">
+        <f>M13/1000</f>
+        <v>498.22399999999999</v>
+      </c>
+      <c r="N9" s="70">
+        <f t="shared" ref="N9:O9" si="2">N13/1000</f>
+        <v>890.572</v>
+      </c>
+      <c r="O9" s="71">
+        <f t="shared" si="2"/>
+        <v>719.18299999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+    </row>
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="L12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+    </row>
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="42">
+        <v>514703</v>
+      </c>
+      <c r="F13" s="42">
+        <v>563758</v>
+      </c>
+      <c r="G13" s="42">
+        <v>890580</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="42">
+        <v>498224</v>
+      </c>
+      <c r="N13" s="42">
+        <v>890572</v>
+      </c>
+      <c r="O13" s="42">
+        <v>719183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="42">
+        <v>357116</v>
+      </c>
+      <c r="F14" s="42">
+        <v>385019</v>
+      </c>
+      <c r="G14" s="42">
+        <v>388669</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="42">
+        <v>272290</v>
+      </c>
+      <c r="N14" s="42">
+        <v>272913</v>
+      </c>
+      <c r="O14" s="42">
+        <v>281776</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="42">
+        <v>100741</v>
+      </c>
+      <c r="F15" s="42">
+        <v>100621</v>
+      </c>
+      <c r="G15" s="42">
+        <v>100640</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="42">
+        <v>5</v>
+      </c>
+      <c r="N15" s="42">
+        <v>5</v>
+      </c>
+      <c r="O15" s="42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="42">
+        <v>234657</v>
+      </c>
+      <c r="F16" s="42">
+        <v>262867</v>
+      </c>
+      <c r="G16" s="42">
+        <v>266218</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="42">
+        <v>159841</v>
+      </c>
+      <c r="N16" s="42">
+        <v>180544</v>
+      </c>
+      <c r="O16" s="42">
+        <v>185422</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="42">
+        <v>54299</v>
+      </c>
+      <c r="F17" s="42">
+        <v>55424</v>
+      </c>
+      <c r="G17" s="42">
+        <v>55233</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="42">
+        <v>8197</v>
+      </c>
+      <c r="N17" s="42">
+        <v>8197</v>
+      </c>
+      <c r="O17" s="42">
+        <v>8197</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="42">
+        <v>40982</v>
+      </c>
+      <c r="F18" s="42">
+        <v>41608</v>
+      </c>
+      <c r="G18" s="42">
+        <v>41228</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="42">
+        <v>8366</v>
+      </c>
+      <c r="F19" s="42">
+        <v>8366</v>
+      </c>
+      <c r="G19" s="42">
+        <v>8366</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="42">
+        <v>8197</v>
+      </c>
+      <c r="F20" s="42">
+        <v>8197</v>
+      </c>
+      <c r="G20" s="42">
+        <v>8197</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="4:15" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L12:O12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6598746-EF65-B94D-A3A6-D9F854046565}">
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="3.83203125" style="9" customWidth="1"/>
     <col min="5" max="10" width="20.83203125" style="9" customWidth="1"/>
-    <col min="11" max="12" width="10.83203125" style="9"/>
-    <col min="13" max="15" width="3.83203125" style="9" customWidth="1"/>
-    <col min="16" max="20" width="20.83203125" style="9" customWidth="1"/>
-    <col min="21" max="16384" width="10.83203125" style="9"/>
+    <col min="11" max="13" width="3.83203125" style="9" customWidth="1"/>
+    <col min="14" max="19" width="20.83203125" style="9" customWidth="1"/>
+    <col min="20" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+    </row>
+    <row r="2" spans="1:21" ht="20" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="42" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G3" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H3" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I3" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="42" t="s">
+      <c r="K3" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="42" t="s">
+      <c r="P3" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="42" t="s">
+      <c r="Q3" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="R3" s="36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="55"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22" t="s">
+    <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="44"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="20">
-        <f>(F11-F12)/1000</f>
+      <c r="F4" s="18">
+        <f>(F13-F14)/1000</f>
         <v>188.505</v>
       </c>
-      <c r="G2" s="17">
-        <f t="shared" ref="G2:H2" si="0">(G11-G12)/1000</f>
+      <c r="G4" s="15">
+        <f t="shared" ref="G4:H4" si="0">(G13-G14)/1000</f>
         <v>1539.193</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H4" s="15">
         <f t="shared" si="0"/>
         <v>4316.2619999999997</v>
       </c>
-      <c r="I2" s="27">
-        <f t="shared" ref="I2" si="1">(I11-I12)/1000</f>
+      <c r="I4" s="24">
+        <f t="shared" ref="I4" si="1">(I13-I14)/1000</f>
         <v>4995.7139999999999</v>
       </c>
-      <c r="M2" s="61" t="s">
+      <c r="K4" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="22" t="s">
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="20">
-        <f>(Q9-Q10)/1000</f>
+      <c r="O4" s="18">
+        <f>(O11-O12)/1000</f>
         <v>258.56799999999998</v>
       </c>
-      <c r="R2" s="20">
-        <f t="shared" ref="R2:T2" si="2">(R9-R10)/1000</f>
+      <c r="P4" s="18">
+        <f t="shared" ref="P4:R4" si="2">(P11-P12)/1000</f>
         <v>4559.6779999999999</v>
       </c>
-      <c r="S2" s="20">
+      <c r="Q4" s="18">
         <f t="shared" si="2"/>
         <v>8795.9699999999993</v>
       </c>
-      <c r="T2" s="20">
+      <c r="R4" s="18">
         <f t="shared" si="2"/>
         <v>11407.457</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+    <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="16">
-        <f>(F12-F13-F14)/1000</f>
+      <c r="F5" s="14">
+        <f>(F14-F15-F16)/1000</f>
         <v>18.111000000000001</v>
       </c>
-      <c r="G3" s="16">
-        <f t="shared" ref="G3:H3" si="3">(G12-G13-G14)/1000</f>
+      <c r="G5" s="14">
+        <f t="shared" ref="G5:H5" si="3">(G14-G15-G16)/1000</f>
         <v>17.454999999999998</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H5" s="14">
         <f t="shared" si="3"/>
         <v>17.045000000000002</v>
       </c>
-      <c r="I3" s="29">
-        <f t="shared" ref="I3" si="4">(I12-I13-I14)/1000</f>
+      <c r="I5" s="25">
+        <f t="shared" ref="I5" si="4">(I14-I15-I16)/1000</f>
         <v>16.754999999999999</v>
       </c>
-      <c r="M3" s="28"/>
-      <c r="N3" s="59" t="s">
+      <c r="K5" s="57"/>
+      <c r="L5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="24"/>
-      <c r="P3" s="25" t="s">
+      <c r="M5" s="22"/>
+      <c r="N5" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="16">
-        <f>(Q10-Q11-Q12)/1000</f>
+      <c r="O5" s="14">
+        <f>(O12-O13-O14)/1000</f>
         <v>71.915999999999997</v>
       </c>
-      <c r="R3" s="16">
-        <f t="shared" ref="R3:T3" si="5">(R10-R11-R12)/1000</f>
+      <c r="P5" s="14">
+        <f t="shared" ref="P5:R5" si="5">(P12-P13-P14)/1000</f>
         <v>90.081999999999994</v>
       </c>
-      <c r="S3" s="16">
+      <c r="Q5" s="14">
         <f t="shared" si="5"/>
         <v>82.808000000000007</v>
       </c>
-      <c r="T3" s="16">
+      <c r="R5" s="14">
         <f t="shared" si="5"/>
         <v>78.724000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="39" t="s">
+    <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="57"/>
+      <c r="B6" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C6" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="38" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="15">
-        <f>F13/1000</f>
+      <c r="F6" s="13">
+        <f>F15/1000</f>
         <v>100.922</v>
       </c>
-      <c r="G4" s="15">
-        <f t="shared" ref="G4:H4" si="6">G13/1000</f>
+      <c r="G6" s="13">
+        <f t="shared" ref="G6:H6" si="6">G15/1000</f>
         <v>103.88</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H6" s="13">
         <f t="shared" si="6"/>
         <v>103.629</v>
       </c>
-      <c r="I4" s="30">
-        <f t="shared" ref="I4" si="7">I13/1000</f>
+      <c r="I6" s="26">
+        <f t="shared" ref="I6" si="7">I15/1000</f>
         <v>103.709</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="28"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="44" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" s="15">
-        <f>Q11/1000</f>
+      <c r="N6" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="13">
+        <f>O13/1000</f>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="R4" s="15">
-        <f t="shared" ref="R4:T4" si="8">R11/1000</f>
+      <c r="P6" s="13">
+        <f t="shared" ref="P6:R6" si="8">P13/1000</f>
         <v>2E-3</v>
       </c>
-      <c r="S4" s="15">
+      <c r="Q6" s="13">
         <f t="shared" si="8"/>
         <v>2E-3</v>
       </c>
-      <c r="T4" s="15">
+      <c r="R6" s="13">
         <f t="shared" si="8"/>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="U4" s="9" t="s">
-        <v>54</v>
-      </c>
     </row>
-    <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="37" t="s">
+    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="57"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="10">
-        <f>(F14-F15)/1000</f>
+      <c r="F7" s="10">
+        <f>(F16-F17)/1000</f>
         <v>151.18</v>
       </c>
-      <c r="G5" s="10">
-        <f t="shared" ref="G5:H5" si="9">(G14-G15)/1000</f>
+      <c r="G7" s="10">
+        <f t="shared" ref="G7:H7" si="9">(G16-G17)/1000</f>
         <v>161.465</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H7" s="10">
         <f t="shared" si="9"/>
         <v>172.553</v>
       </c>
-      <c r="I5" s="31">
-        <f t="shared" ref="I5" si="10">(I14-I15)/1000</f>
+      <c r="I7" s="27">
+        <f t="shared" ref="I7" si="10">(I16-I17)/1000</f>
         <v>174.63900000000001</v>
       </c>
-      <c r="M5" s="28"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>Q12/1000</f>
+      <c r="K7" s="57"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="10">
+        <f>O14/1000</f>
         <v>132.22800000000001</v>
       </c>
-      <c r="R5" s="10">
-        <f t="shared" ref="R5:T5" si="11">R12/1000</f>
+      <c r="P7" s="10">
+        <f t="shared" ref="P7:R7" si="11">P14/1000</f>
         <v>483.22199999999998</v>
       </c>
-      <c r="S5" s="10">
+      <c r="Q7" s="10">
         <f t="shared" si="11"/>
         <v>832.16600000000005</v>
       </c>
-      <c r="T5" s="10">
+      <c r="R7" s="10">
         <f t="shared" si="11"/>
         <v>1144.797</v>
       </c>
-      <c r="U5" s="9" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="6" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="18" t="s">
+    <row r="8" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="57"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="19">
-        <f>(F15-F16)/1000</f>
+      <c r="F8" s="17">
+        <f>(F17-F18)/1000</f>
         <v>5.5709999999999997</v>
       </c>
-      <c r="G6" s="19">
-        <f t="shared" ref="G6:H6" si="12">(G15-G16)/1000</f>
+      <c r="G8" s="17">
+        <f t="shared" ref="G8:H8" si="12">(G17-G18)/1000</f>
         <v>62.759</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H8" s="17">
         <f t="shared" si="12"/>
         <v>131.67699999999999</v>
       </c>
-      <c r="I6" s="32">
-        <f t="shared" ref="I6" si="13">(I15-I16)/1000</f>
+      <c r="I8" s="28">
+        <f t="shared" ref="I8" si="13">(I17-I18)/1000</f>
         <v>149.59100000000001</v>
       </c>
-      <c r="M6" s="34"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="35">
-        <f>Q5/Q13</f>
+      <c r="K8" s="58"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="O8" s="30">
+        <f>O7/O15</f>
         <v>1.6050983248361253E-2</v>
       </c>
-      <c r="R6" s="35">
-        <f>R5/R13</f>
+      <c r="P8" s="30">
+        <f>P7/P15</f>
         <v>1.7756832137227018E-3</v>
       </c>
-      <c r="S6" s="35">
-        <f>S5/S13</f>
+      <c r="Q8" s="30">
+        <f>Q7/Q15</f>
         <v>1.5575553505017062E-3</v>
       </c>
-      <c r="T6" s="35">
-        <f>T5/T13</f>
+      <c r="R8" s="30">
+        <f>R7/R15</f>
         <v>1.4373782092490658E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="13" t="s">
+    <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="57"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="14">
-        <f>F16/1000</f>
+      <c r="F9" s="12">
+        <f>F18/1000</f>
         <v>19.068999999999999</v>
       </c>
-      <c r="G7" s="14">
-        <f t="shared" ref="G7:H7" si="14">G16/1000</f>
+      <c r="G9" s="12">
+        <f t="shared" ref="G9:H9" si="14">G18/1000</f>
         <v>626.89499999999998</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H9" s="12">
         <f t="shared" si="14"/>
         <v>1238.579</v>
       </c>
-      <c r="I7" s="33">
-        <f t="shared" ref="I7" si="15">I16/1000</f>
+      <c r="I9" s="29">
+        <f t="shared" ref="I9" si="15">I18/1000</f>
         <v>1819.8589999999999</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="8" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="41" t="s">
+    <row r="10" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="58"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="35">
-        <f>F7/F18</f>
+      <c r="F10" s="30">
+        <f>F9/F20</f>
         <v>2.3147608642874484E-3</v>
       </c>
-      <c r="G8" s="35">
-        <f t="shared" ref="G8:I8" si="16">G7/G18</f>
+      <c r="G10" s="30">
+        <f t="shared" ref="G10:I10" si="16">G9/G20</f>
         <v>2.303634619836624E-3</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H10" s="30">
         <f t="shared" si="16"/>
         <v>2.318233800070001E-3</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I10" s="31">
         <f t="shared" si="16"/>
         <v>2.2849690124151232E-3</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="N10" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-    </row>
-    <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I9" s="51"/>
-      <c r="J9" s="52"/>
-      <c r="P9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q9" s="53">
-        <v>462715</v>
-      </c>
-      <c r="R9" s="53">
-        <v>5132984</v>
-      </c>
-      <c r="S9" s="53">
-        <v>9710946</v>
-      </c>
-      <c r="T9" s="53">
-        <v>12630981</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="P10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q10" s="53">
-        <v>204147</v>
-      </c>
-      <c r="R10" s="53">
-        <v>573306</v>
-      </c>
-      <c r="S10" s="53">
-        <v>914976</v>
-      </c>
-      <c r="T10" s="53">
-        <v>1223524</v>
-      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="53">
-        <v>483358</v>
-      </c>
-      <c r="G11" s="53">
-        <v>2511647</v>
-      </c>
-      <c r="H11" s="53">
-        <v>5979745</v>
-      </c>
-      <c r="I11" s="53">
-        <v>7260267</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="53">
-        <v>3</v>
-      </c>
-      <c r="R11" s="53">
-        <v>2</v>
-      </c>
-      <c r="S11" s="53">
-        <v>2</v>
-      </c>
-      <c r="T11" s="53">
-        <v>3</v>
+      <c r="I11" s="41"/>
+      <c r="N11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" s="42">
+        <v>462715</v>
+      </c>
+      <c r="P11" s="42">
+        <v>5132984</v>
+      </c>
+      <c r="Q11" s="42">
+        <v>9710946</v>
+      </c>
+      <c r="R11" s="42">
+        <v>12630981</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="53">
-        <v>294853</v>
-      </c>
-      <c r="G12" s="53">
-        <v>972454</v>
-      </c>
-      <c r="H12" s="53">
-        <v>1663483</v>
-      </c>
-      <c r="I12" s="53">
-        <v>2264553</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q12" s="53">
-        <v>132228</v>
-      </c>
-      <c r="R12" s="53">
-        <v>483222</v>
-      </c>
-      <c r="S12" s="53">
-        <v>832166</v>
-      </c>
-      <c r="T12" s="53">
-        <v>1144797</v>
+      <c r="E12" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="N12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="42">
+        <v>204147</v>
+      </c>
+      <c r="P12" s="42">
+        <v>573306</v>
+      </c>
+      <c r="Q12" s="42">
+        <v>914976</v>
+      </c>
+      <c r="R12" s="42">
+        <v>1223524</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="53">
-        <v>100922</v>
-      </c>
-      <c r="G13" s="53">
-        <v>103880</v>
-      </c>
-      <c r="H13" s="53">
-        <v>103629</v>
-      </c>
-      <c r="I13" s="53">
-        <v>103709</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="53">
-        <v>8238</v>
-      </c>
-      <c r="R13" s="53">
-        <v>272133</v>
-      </c>
-      <c r="S13" s="53">
-        <v>534277</v>
-      </c>
-      <c r="T13" s="53">
-        <v>796448</v>
+        <v>27</v>
+      </c>
+      <c r="F13" s="42">
+        <v>483358</v>
+      </c>
+      <c r="G13" s="42">
+        <v>2511647</v>
+      </c>
+      <c r="H13" s="42">
+        <v>5979745</v>
+      </c>
+      <c r="I13" s="42">
+        <v>7260267</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="42">
+        <v>3</v>
+      </c>
+      <c r="P13" s="42">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="42">
+        <v>2</v>
+      </c>
+      <c r="R13" s="42">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="53">
-        <v>175820</v>
-      </c>
-      <c r="G14" s="53">
-        <v>851119</v>
-      </c>
-      <c r="H14" s="53">
-        <v>1542809</v>
-      </c>
-      <c r="I14" s="53">
-        <v>2144089</v>
+        <v>28</v>
+      </c>
+      <c r="F14" s="42">
+        <v>294853</v>
+      </c>
+      <c r="G14" s="42">
+        <v>972454</v>
+      </c>
+      <c r="H14" s="42">
+        <v>1663483</v>
+      </c>
+      <c r="I14" s="42">
+        <v>2264553</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O14" s="42">
+        <v>132228</v>
+      </c>
+      <c r="P14" s="42">
+        <v>483222</v>
+      </c>
+      <c r="Q14" s="42">
+        <v>832166</v>
+      </c>
+      <c r="R14" s="42">
+        <v>1144797</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="53">
-        <v>24640</v>
-      </c>
-      <c r="G15" s="53">
-        <v>689654</v>
-      </c>
-      <c r="H15" s="53">
-        <v>1370256</v>
-      </c>
-      <c r="I15" s="53">
-        <v>1969450</v>
+        <v>29</v>
+      </c>
+      <c r="F15" s="42">
+        <v>100922</v>
+      </c>
+      <c r="G15" s="42">
+        <v>103880</v>
+      </c>
+      <c r="H15" s="42">
+        <v>103629</v>
+      </c>
+      <c r="I15" s="42">
+        <v>103709</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O15" s="42">
+        <v>8238</v>
+      </c>
+      <c r="P15" s="42">
+        <v>272133</v>
+      </c>
+      <c r="Q15" s="42">
+        <v>534277</v>
+      </c>
+      <c r="R15" s="42">
+        <v>796448</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E16" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="53">
-        <v>19069</v>
-      </c>
-      <c r="G16" s="53">
-        <v>626895</v>
-      </c>
-      <c r="H16" s="53">
-        <v>1238579</v>
-      </c>
-      <c r="I16" s="53">
-        <v>1819859</v>
+        <v>30</v>
+      </c>
+      <c r="F16" s="42">
+        <v>175820</v>
+      </c>
+      <c r="G16" s="42">
+        <v>851119</v>
+      </c>
+      <c r="H16" s="42">
+        <v>1542809</v>
+      </c>
+      <c r="I16" s="42">
+        <v>2144089</v>
       </c>
     </row>
     <row r="17" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="53">
-        <v>8413</v>
-      </c>
-      <c r="G17" s="53">
-        <v>272463</v>
-      </c>
-      <c r="H17" s="53">
-        <v>534609</v>
-      </c>
-      <c r="I17" s="53">
-        <v>796781</v>
+        <v>31</v>
+      </c>
+      <c r="F17" s="42">
+        <v>24640</v>
+      </c>
+      <c r="G17" s="42">
+        <v>689654</v>
+      </c>
+      <c r="H17" s="42">
+        <v>1370256</v>
+      </c>
+      <c r="I17" s="42">
+        <v>1969450</v>
       </c>
     </row>
     <row r="18" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="42">
+        <v>19069</v>
+      </c>
+      <c r="G18" s="42">
+        <v>626895</v>
+      </c>
+      <c r="H18" s="42">
+        <v>1238579</v>
+      </c>
+      <c r="I18" s="42">
+        <v>1819859</v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="42">
+        <v>8413</v>
+      </c>
+      <c r="G19" s="42">
+        <v>272463</v>
+      </c>
+      <c r="H19" s="42">
+        <v>534609</v>
+      </c>
+      <c r="I19" s="42">
+        <v>796781</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F20" s="42">
         <v>8238</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G20" s="42">
         <v>272133</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H20" s="42">
         <v>534277</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I20" s="42">
         <v>796448</v>
       </c>
     </row>
-    <row r="19" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="5:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="P8:T8"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="O4:O6"/>
-    <mergeCell ref="N3:N6"/>
-    <mergeCell ref="M2:M6"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="11">
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="K4:K8"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="A5:A10"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="F4" formula="1"/>
+    <ignoredError sqref="F6" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1EE695-0A37-4944-9262-B53A47FF3098}">
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19419,12 +21949,12 @@
       <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
@@ -19729,7 +22259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6EFC72-B432-1B4C-B65F-277D1C452C6D}">
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
